--- a/business_forms/042_project_completion_form--business_forms.xlsx
+++ b/business_forms/042_project_completion_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1262,17 +1262,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_member_choices</t>
+          <t>client_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>johndoe</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JohnDoe</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>client_choices</t>
+          <t>project_manager_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>project_manager_choices</t>
+          <t>project_team_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>project_team_choices</t>
+          <t>project_location_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>project_location_choices</t>
+          <t>project_approval_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>notapproved</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>NotApproved</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>notapproved</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NotApproved</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>project_approval_status_choices</t>
+          <t>project_reviewer_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>project_reviewer_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>project_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>project_status_2_choices</t>
+          <t>project_outcome_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>project_outcome_2_choices</t>
+          <t>project_location_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1607,27 +1607,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>project_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
